--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelByWire.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelByWire.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD727805-6209-4FE0-A262-2E69C1B854DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7368A7-16B6-4A56-A1E1-7E97B8C39578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29385" yWindow="0" windowWidth="26910" windowHeight="15585" tabRatio="940" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="6135" yWindow="465" windowWidth="21600" windowHeight="13230" tabRatio="940" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="RWhlByW_Hamba_f" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="62">
   <si>
     <t>Units</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>DHousing</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,49 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -771,7 +816,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -916,41 +961,41 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="19">
-        <v>100000</v>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -961,200 +1006,197 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="19">
-        <v>5.0000000000000001E-3</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="19">
-        <v>100</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="11">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0.37675517503754502</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0.92326153885340301</v>
+        <v>53</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F14" s="11">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0.37675517503754502</v>
+      </c>
       <c r="H14" s="11">
-        <v>0.35289999999999999</v>
+        <v>0.92326153885340301</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>20</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0.01</v>
-      </c>
-      <c r="J17">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>16000</v>
+        <v>0.01</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
-        <v>500</v>
+        <v>8000</v>
+      </c>
+      <c r="I19">
+        <v>16000</v>
+      </c>
+      <c r="J19">
+        <v>16000</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4"/>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="16">
-        <v>1000</v>
+      <c r="H21" s="6">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" t="s">
@@ -1172,279 +1214,290 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C23" s="4"/>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6">
-        <v>0.5</v>
+      <c r="H23" s="16">
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="4"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="4"/>
-      <c r="D24" t="s">
-        <v>37</v>
+      <c r="E24" t="s">
+        <v>35</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6">
-        <v>48</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
-      </c>
-      <c r="K25" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1800</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="K26" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6">
-        <v>50</v>
+        <v>1800</v>
+      </c>
+      <c r="I27">
+        <v>1800</v>
+      </c>
+      <c r="J27">
+        <v>1400</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
-        <v>45</v>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>300</v>
-      </c>
-      <c r="K30" s="6">
-        <v>500</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="K31" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
-        <v>1000</v>
+        <v>1800</v>
+      </c>
+      <c r="I32">
+        <v>1800</v>
+      </c>
+      <c r="J32">
+        <v>1400</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
-        <v>45</v>
+      <c r="B33" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" t="s">
+        <v>49</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="H35" s="6">
+        <v>1.0000000000000001E-5</v>
+      </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="11"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H38" s="11"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
+      <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
     </row>
@@ -1452,12 +1505,10 @@
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="13"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -1470,64 +1521,83 @@
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="13"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="13"/>
-      <c r="H49" s="14"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50" s="13"/>
       <c r="H50" s="14"/>
     </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" s="13"/>
+      <c r="H51" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A49:A50">
-    <cfRule type="cellIs" dxfId="16" priority="15" operator="equal">
+  <conditionalFormatting sqref="A50:A51">
+    <cfRule type="cellIs" dxfId="22" priority="17" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B18 E7:E23">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:B7 E7 E9:E24 A9:B19">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45:B48">
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+  <conditionalFormatting sqref="A46:B49">
+    <cfRule type="cellIs" dxfId="20" priority="19" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:C24">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+  <conditionalFormatting sqref="A20:C25">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+  <conditionalFormatting sqref="E28">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="E33">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1540,7 +1610,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1679,41 +1749,41 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="19">
-        <v>100000</v>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -1724,200 +1794,197 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="19">
-        <v>5.0000000000000001E-3</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="19">
-        <v>100</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="6">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0.88921153885340298</v>
+        <v>53</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11">
-        <v>0.35289999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>20</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0.01</v>
-      </c>
-      <c r="J17">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>16000</v>
+        <v>0.01</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
-        <v>500</v>
+        <v>8000</v>
+      </c>
+      <c r="I19">
+        <v>16000</v>
+      </c>
+      <c r="J19">
+        <v>16000</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4"/>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="16">
-        <v>1000</v>
+      <c r="H21" s="6">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" t="s">
@@ -1935,256 +2002,284 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C23" s="4"/>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6">
-        <v>0.5</v>
+      <c r="H23" s="16">
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="4"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="4"/>
-      <c r="D24" t="s">
-        <v>37</v>
+      <c r="E24" t="s">
+        <v>35</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6">
-        <v>48</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
-      </c>
-      <c r="K25" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1800</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="K26" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6">
-        <v>50</v>
+        <v>1800</v>
+      </c>
+      <c r="I27">
+        <v>1800</v>
+      </c>
+      <c r="J27">
+        <v>1400</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
-        <v>45</v>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>300</v>
-      </c>
-      <c r="K30" s="6">
-        <v>500</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="K31" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
-        <v>50</v>
+        <v>1800</v>
+      </c>
+      <c r="I32">
+        <v>1800</v>
+      </c>
+      <c r="J32">
+        <v>1400</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
-        <v>45</v>
+      <c r="B33" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:B18 E7:E23">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:B7 E7 E9:E24 A9:B19">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:C24">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+  <conditionalFormatting sqref="A20:C25">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+  <conditionalFormatting sqref="E28">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+  <conditionalFormatting sqref="E33">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2197,7 +2292,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -2336,41 +2431,41 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="19">
-        <v>100000</v>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -2381,200 +2476,197 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="19">
-        <v>5.0000000000000001E-3</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="19">
-        <v>100</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="11">
-        <v>1.18</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0.55926517503754503</v>
-      </c>
-      <c r="H13" s="11">
-        <v>1.34</v>
+        <v>53</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1.18</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0.55926517503754503</v>
+      </c>
       <c r="H14" s="11">
-        <v>0.78888879999999995</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11">
-        <v>1</v>
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>20</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0.01</v>
-      </c>
-      <c r="J17">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>16000</v>
+        <v>0.01</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6">
-        <v>500</v>
+        <v>8000</v>
+      </c>
+      <c r="I19">
+        <v>16000</v>
+      </c>
+      <c r="J19">
+        <v>16000</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4"/>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="16">
-        <v>1000</v>
+      <c r="H21" s="6">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" t="s">
@@ -2592,256 +2684,284 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C23" s="4"/>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6">
-        <v>0.5</v>
+      <c r="H23" s="16">
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="4"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="C24" s="4"/>
-      <c r="D24" t="s">
-        <v>37</v>
+      <c r="E24" t="s">
+        <v>35</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6">
-        <v>48</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
-      </c>
-      <c r="K25" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>1800</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="K26" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6">
-        <v>50</v>
+        <v>1800</v>
+      </c>
+      <c r="I27">
+        <v>1800</v>
+      </c>
+      <c r="J27">
+        <v>1400</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
-        <v>45</v>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6">
-        <v>1.0000000000000001E-5</v>
+        <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>300</v>
-      </c>
-      <c r="K30" s="6">
-        <v>500</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="K31" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6">
-        <v>50</v>
+        <v>1800</v>
+      </c>
+      <c r="I32">
+        <v>1800</v>
+      </c>
+      <c r="J32">
+        <v>1400</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
-        <v>45</v>
+      <c r="B33" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6">
-        <v>5.0000000000000004E-6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6">
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:B18 E7:E23">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:B7 E7 E9:E24 A9:B19">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:C24">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+  <conditionalFormatting sqref="A20:C25">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="E28">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="E33">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
